--- a/initial_descriptive_analysis/output/sample_description/csv/en_sociodemographic_by_archetype_for_word.xlsx
+++ b/initial_descriptive_analysis/output/sample_description/csv/en_sociodemographic_by_archetype_for_word.xlsx
@@ -32,7 +32,7 @@
     <t xml:space="preserve">Homo economicus</t>
   </si>
   <si>
-    <t xml:space="preserve">Sentient</t>
+    <t xml:space="preserve">Stubborn</t>
   </si>
   <si>
     <t xml:space="preserve">Influencer</t>
